--- a/salidas/empresas/BDX.xlsx
+++ b/salidas/empresas/BDX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>34.90282821655273</v>
+        <v>34.90283966064453</v>
       </c>
       <c r="C2" t="n">
         <v>49.70087432861328</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>34.39113998413086</v>
+        <v>34.39115142822266</v>
       </c>
       <c r="C3" t="n">
         <v>48.97223663330078</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28262329101562</v>
+        <v>33.28261566162109</v>
       </c>
       <c r="C4" t="n">
         <v>47.23117065429688</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>34.07169723510742</v>
+        <v>34.07171630859375</v>
       </c>
       <c r="C5" t="n">
         <v>48.35097503662109</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>32.66105651855469</v>
+        <v>32.66106414794922</v>
       </c>
       <c r="C6" t="n">
         <v>46.3491325378418</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.15696334838867</v>
+        <v>33.15693664550781</v>
       </c>
       <c r="C7" t="n">
         <v>46.88602447509766</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.75505065917969</v>
+        <v>35.75504684448242</v>
       </c>
       <c r="C8" t="n">
         <v>50.55990219116211</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>37.80532836914062</v>
+        <v>37.80532455444336</v>
       </c>
       <c r="C9" t="n">
         <v>53.4591178894043</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>38.44998168945312</v>
+        <v>38.44999694824219</v>
       </c>
       <c r="C10" t="n">
         <v>54.20309829711914</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.10176849365234</v>
+        <v>38.10178756713867</v>
       </c>
       <c r="C11" t="n">
         <v>53.71222686767578</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.02126693725586</v>
+        <v>39.02127075195312</v>
       </c>
       <c r="C12" t="n">
         <v>55.00843811035156</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>38.29552459716797</v>
+        <v>38.29553604125977</v>
       </c>
       <c r="C13" t="n">
         <v>53.80426406860352</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.00225067138672</v>
+        <v>42.00226211547852</v>
       </c>
       <c r="C14" t="n">
         <v>59.01211929321289</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>41.4618034362793</v>
+        <v>41.46181488037109</v>
       </c>
       <c r="C15" t="n">
         <v>58.25279998779297</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.11342620849609</v>
+        <v>42.1134147644043</v>
       </c>
       <c r="C16" t="n">
         <v>58.97377014160156</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>43.09929656982422</v>
+        <v>43.09930419921875</v>
       </c>
       <c r="C17" t="n">
         <v>60.35434722900391</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.76287841796875</v>
+        <v>41.76288986206055</v>
       </c>
       <c r="C18" t="n">
         <v>58.48289489746094</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>40.93717956542969</v>
+        <v>40.93716049194336</v>
       </c>
       <c r="C19" t="n">
         <v>57.14066696166992</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.95922088623047</v>
+        <v>41.95922470092773</v>
       </c>
       <c r="C20" t="n">
         <v>58.56726455688477</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>45.22970581054688</v>
+        <v>45.22970199584961</v>
       </c>
       <c r="C22" t="n">
         <v>62.93143081665039</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.0069580078125</v>
+        <v>46.00695419311523</v>
       </c>
       <c r="C23" t="n">
         <v>64.01288604736328</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>45.60456085205078</v>
+        <v>45.60454940795898</v>
       </c>
       <c r="C24" t="n">
         <v>63.45298385620117</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>46.23247528076172</v>
+        <v>46.23249053955078</v>
       </c>
       <c r="C25" t="n">
         <v>64.10492706298828</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>47.81448745727539</v>
+        <v>47.81449508666992</v>
       </c>
       <c r="C26" t="n">
         <v>66.29851531982422</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.01602935791016</v>
+        <v>50.01604080200195</v>
       </c>
       <c r="C27" t="n">
         <v>69.35112762451172</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>49.61010360717773</v>
+        <v>49.61009979248047</v>
       </c>
       <c r="C29" t="n">
         <v>68.56880187988281</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>46.86323928833008</v>
+        <v>46.86322402954102</v>
       </c>
       <c r="C30" t="n">
         <v>64.77220153808594</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>47.27865600585938</v>
+        <v>47.27867126464844</v>
       </c>
       <c r="C32" t="n">
         <v>65.12501525878906</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>48.65398025512695</v>
+        <v>48.65398406982422</v>
       </c>
       <c r="C33" t="n">
         <v>67.01948547363281</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>44.83848190307617</v>
+        <v>44.83847427368164</v>
       </c>
       <c r="C34" t="n">
         <v>61.55852127075195</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.7713737487793</v>
+        <v>38.77136993408203</v>
       </c>
       <c r="C35" t="n">
         <v>53.22902297973633</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>35.49201583862305</v>
+        <v>35.49200439453125</v>
       </c>
       <c r="C36" t="n">
         <v>48.72679901123047</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.40852355957031</v>
+        <v>38.40851211547852</v>
       </c>
       <c r="C37" t="n">
         <v>52.45436477661133</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>40.81221771240234</v>
+        <v>40.81220245361328</v>
       </c>
       <c r="C38" t="n">
         <v>55.73707580566406</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>34.758056640625</v>
+        <v>34.75805282592773</v>
       </c>
       <c r="C39" t="n">
         <v>47.46893692016602</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>34.14236450195312</v>
+        <v>34.14237594604492</v>
       </c>
       <c r="C41" t="n">
         <v>46.38748168945312</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>38.20695114135742</v>
+        <v>38.20693969726562</v>
       </c>
       <c r="C42" t="n">
         <v>51.9098014831543</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>40.45388412475586</v>
+        <v>40.45386505126953</v>
       </c>
       <c r="C43" t="n">
         <v>54.6939697265625</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>36.95934295654297</v>
+        <v>36.95932769775391</v>
       </c>
       <c r="C44" t="n">
         <v>49.96931838989258</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.96672439575195</v>
+        <v>38.96671676635742</v>
       </c>
       <c r="C47" t="n">
         <v>52.43135452270508</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.63764190673828</v>
+        <v>42.63766479492188</v>
       </c>
       <c r="C48" t="n">
         <v>57.37076187133789</v>
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>44.60200119018555</v>
+        <v>44.60200881958008</v>
       </c>
       <c r="C51" t="n">
         <v>59.72541809082031</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>45.30785369873047</v>
+        <v>45.3078727722168</v>
       </c>
       <c r="C52" t="n">
         <v>60.38502883911133</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>43.94974517822266</v>
+        <v>43.94973373413086</v>
       </c>
       <c r="C53" t="n">
         <v>58.57493591308594</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.03202056884766</v>
+        <v>41.03203201293945</v>
       </c>
       <c r="C54" t="n">
         <v>54.68630218505859</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>39.12078857421875</v>
+        <v>39.12078475952148</v>
       </c>
       <c r="C55" t="n">
         <v>51.86378479003906</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.803466796875</v>
+        <v>39.80345153808594</v>
       </c>
       <c r="C56" t="n">
         <v>52.76882934570312</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>39.45055389404297</v>
+        <v>39.4505615234375</v>
       </c>
       <c r="C57" t="n">
         <v>52.30096435546875</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>45.32299423217773</v>
+        <v>45.32297897338867</v>
       </c>
       <c r="C60" t="n">
         <v>59.77143859863281</v>
@@ -1703,11 +1715,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>49.40454483032227</v>
+        <v>49.404541015625</v>
       </c>
       <c r="C61" t="n">
         <v>64.82589721679688</v>
@@ -1732,11 +1744,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>48.48682022094727</v>
+        <v>48.48681259155273</v>
       </c>
       <c r="C62" t="n">
         <v>63.62171936035156</v>
@@ -1761,11 +1773,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>46.76247024536133</v>
+        <v>46.76246643066406</v>
       </c>
       <c r="C63" t="n">
         <v>61.35910415649414</v>
@@ -1790,11 +1802,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>46.78187942504883</v>
+        <v>46.78188323974609</v>
       </c>
       <c r="C64" t="n">
         <v>61.06764984130859</v>
@@ -1819,11 +1831,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>50.49527740478516</v>
+        <v>50.49528503417969</v>
       </c>
       <c r="C65" t="n">
         <v>65.91501617431641</v>
@@ -1848,7 +1860,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1877,11 +1889,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.87520599365234</v>
+        <v>50.87521743774414</v>
       </c>
       <c r="C67" t="n">
         <v>66.09142303466797</v>
@@ -1906,11 +1918,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>49.36377716064453</v>
+        <v>49.36378860473633</v>
       </c>
       <c r="C68" t="n">
         <v>64.12793731689453</v>
@@ -1935,11 +1947,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>48.04717254638672</v>
+        <v>48.04718399047852</v>
       </c>
       <c r="C69" t="n">
         <v>62.41754913330078</v>
@@ -1964,11 +1976,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>43.5160026550293</v>
+        <v>43.5159797668457</v>
       </c>
       <c r="C70" t="n">
         <v>56.23561859130859</v>
@@ -1993,11 +2005,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>46.43011474609375</v>
+        <v>46.43011856079102</v>
       </c>
       <c r="C71" t="n">
         <v>60.00153350830078</v>
@@ -2022,11 +2034,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>43.78900146484375</v>
+        <v>43.78900909423828</v>
       </c>
       <c r="C72" t="n">
         <v>56.58843231201172</v>
@@ -2051,11 +2063,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>44.61778259277344</v>
+        <v>44.61777877807617</v>
       </c>
       <c r="C73" t="n">
         <v>57.30940246582031</v>
@@ -2080,11 +2092,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.82121658325195</v>
+        <v>46.82120513916016</v>
       </c>
       <c r="C74" t="n">
         <v>60.13959121704102</v>
@@ -2109,11 +2121,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.51348876953125</v>
+        <v>45.51349258422852</v>
       </c>
       <c r="C75" t="n">
         <v>58.45988464355469</v>
@@ -2138,7 +2150,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2167,11 +2179,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>47.12620162963867</v>
+        <v>47.12620544433594</v>
       </c>
       <c r="C77" t="n">
         <v>60.17027282714844</v>
@@ -2196,11 +2208,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.93039703369141</v>
+        <v>43.93038940429688</v>
       </c>
       <c r="C78" t="n">
         <v>56.08988952636719</v>
@@ -2225,11 +2237,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>45.18364334106445</v>
+        <v>45.18366622924805</v>
       </c>
       <c r="C79" t="n">
         <v>57.33241271972656</v>
@@ -2254,11 +2266,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>45.76393508911133</v>
+        <v>45.76394271850586</v>
       </c>
       <c r="C80" t="n">
         <v>58.06872177124023</v>
@@ -2283,7 +2295,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2312,11 +2324,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>47.7673454284668</v>
+        <v>47.76735305786133</v>
       </c>
       <c r="C82" t="n">
         <v>60.254638671875</v>
@@ -2341,11 +2353,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>46.01620101928711</v>
+        <v>46.01620483398438</v>
       </c>
       <c r="C83" t="n">
         <v>58.04571151733398</v>
@@ -2370,11 +2382,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>46.61817169189453</v>
+        <v>46.6181526184082</v>
       </c>
       <c r="C84" t="n">
         <v>58.80503082275391</v>
@@ -2399,11 +2411,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>47.84841918945312</v>
+        <v>47.84842300415039</v>
       </c>
       <c r="C85" t="n">
         <v>59.97085571289062</v>
@@ -2428,11 +2440,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>51.42832946777344</v>
+        <v>51.42832565307617</v>
       </c>
       <c r="C86" t="n">
         <v>64.45774078369141</v>
@@ -2457,11 +2469,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>53.88836669921875</v>
+        <v>53.88835906982422</v>
       </c>
       <c r="C87" t="n">
         <v>67.54103088378906</v>
@@ -2486,11 +2498,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.83514022827148</v>
+        <v>58.83513259887695</v>
       </c>
       <c r="C88" t="n">
         <v>73.33180236816406</v>
@@ -2515,11 +2527,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>58.02900314331055</v>
+        <v>58.02898406982422</v>
       </c>
       <c r="C89" t="n">
         <v>72.32704162597656</v>
@@ -2544,11 +2556,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>60.6873779296875</v>
+        <v>60.68738555908203</v>
       </c>
       <c r="C90" t="n">
         <v>75.64043426513672</v>
@@ -2573,11 +2585,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.12417984008789</v>
+        <v>61.12417602539062</v>
       </c>
       <c r="C91" t="n">
         <v>75.80150604248047</v>
@@ -2602,11 +2614,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>64.14856719970703</v>
+        <v>64.14855194091797</v>
       </c>
       <c r="C92" t="n">
         <v>79.55207824707031</v>
@@ -2631,11 +2643,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>60.22738647460938</v>
+        <v>60.22737121582031</v>
       </c>
       <c r="C93" t="n">
         <v>74.68936920166016</v>
@@ -2660,11 +2672,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.17191696166992</v>
+        <v>62.17192840576172</v>
       </c>
       <c r="C94" t="n">
         <v>76.71421813964844</v>
@@ -2689,11 +2701,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.34824371337891</v>
+        <v>65.3482666015625</v>
       </c>
       <c r="C95" t="n">
         <v>80.63352966308594</v>
@@ -2718,7 +2730,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2747,11 +2759,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>69.03162384033203</v>
+        <v>69.03164672851562</v>
       </c>
       <c r="C97" t="n">
         <v>84.74459075927734</v>
@@ -2776,11 +2788,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>67.55091857910156</v>
+        <v>67.55088043212891</v>
       </c>
       <c r="C98" t="n">
         <v>82.92682647705078</v>
@@ -2805,11 +2817,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>71.98683166503906</v>
+        <v>71.98682403564453</v>
       </c>
       <c r="C99" t="n">
         <v>88.37245178222656</v>
@@ -2834,11 +2846,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>73.49337768554688</v>
+        <v>73.49336242675781</v>
       </c>
       <c r="C100" t="n">
         <v>89.79904937744141</v>
@@ -2863,11 +2875,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>70.95111083984375</v>
+        <v>70.95111846923828</v>
       </c>
       <c r="C101" t="n">
         <v>86.69274139404297</v>
@@ -2892,11 +2904,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.882568359375</v>
+        <v>73.88255310058594</v>
       </c>
       <c r="C102" t="n">
         <v>90.27458190917969</v>
@@ -2921,11 +2933,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>74.6002197265625</v>
+        <v>74.60020446777344</v>
       </c>
       <c r="C103" t="n">
         <v>90.73477172851562</v>
@@ -2950,11 +2962,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>73.30119323730469</v>
+        <v>73.30118560791016</v>
       </c>
       <c r="C104" t="n">
         <v>89.15477752685547</v>
@@ -2979,11 +2991,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>73.88763427734375</v>
+        <v>73.88762664794922</v>
       </c>
       <c r="C105" t="n">
         <v>89.86808013916016</v>
@@ -3008,11 +3020,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>72.10638427734375</v>
+        <v>72.10637664794922</v>
       </c>
       <c r="C106" t="n">
         <v>87.29099273681641</v>
@@ -3037,11 +3049,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>81.54019927978516</v>
+        <v>81.54016876220703</v>
       </c>
       <c r="C107" t="n">
         <v>98.71145629882812</v>
@@ -3066,11 +3078,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>88.90858459472656</v>
+        <v>88.90859985351562</v>
       </c>
       <c r="C108" t="n">
         <v>107.6315383911133</v>
@@ -3095,7 +3107,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3124,11 +3136,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>87.86191558837891</v>
+        <v>87.86190795898438</v>
       </c>
       <c r="C110" t="n">
         <v>105.9058151245117</v>
@@ -3153,11 +3165,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>93.35962677001953</v>
+        <v>93.35966491699219</v>
       </c>
       <c r="C111" t="n">
         <v>112.532600402832</v>
@@ -3182,11 +3194,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>91.73617553710938</v>
+        <v>91.73616027832031</v>
       </c>
       <c r="C112" t="n">
         <v>110.1319198608398</v>
@@ -3211,11 +3223,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>89.9984130859375</v>
+        <v>89.99842071533203</v>
       </c>
       <c r="C113" t="n">
         <v>108.0457153320312</v>
@@ -3240,11 +3252,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>89.76841735839844</v>
+        <v>89.7684326171875</v>
       </c>
       <c r="C114" t="n">
         <v>107.7695999145508</v>
@@ -3269,11 +3281,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>90.88574981689453</v>
+        <v>90.88573455810547</v>
       </c>
       <c r="C115" t="n">
         <v>108.6439666748047</v>
@@ -3298,11 +3310,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>97.62274932861328</v>
+        <v>97.62276458740234</v>
       </c>
       <c r="C116" t="n">
         <v>116.6973495483398</v>
@@ -3327,11 +3339,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>90.48148345947266</v>
+        <v>90.48150634765625</v>
       </c>
       <c r="C117" t="n">
         <v>108.160758972168</v>
@@ -3356,11 +3368,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>85.49325561523438</v>
+        <v>85.49324798583984</v>
       </c>
       <c r="C118" t="n">
         <v>101.7487335205078</v>
@@ -3385,11 +3397,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>91.84756469726562</v>
+        <v>91.84757232666016</v>
       </c>
       <c r="C119" t="n">
         <v>109.3112411499023</v>
@@ -3414,11 +3426,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>96.8292236328125</v>
+        <v>96.82920837402344</v>
       </c>
       <c r="C120" t="n">
         <v>115.2400665283203</v>
@@ -3443,7 +3455,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3472,11 +3484,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>94.08848571777344</v>
+        <v>94.0885009765625</v>
       </c>
       <c r="C122" t="n">
         <v>111.4971618652344</v>
@@ -3501,11 +3513,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>95.43475341796875</v>
+        <v>95.43476867675781</v>
       </c>
       <c r="C123" t="n">
         <v>113.0924987792969</v>
@@ -3530,11 +3542,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>98.70128631591797</v>
+        <v>98.7012939453125</v>
       </c>
       <c r="C124" t="n">
         <v>116.4442367553711</v>
@@ -3559,7 +3571,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3588,11 +3600,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>108.2125625610352</v>
+        <v>108.2125473022461</v>
       </c>
       <c r="C126" t="n">
         <v>127.665283203125</v>
@@ -3617,11 +3629,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>110.683708190918</v>
+        <v>110.6837005615234</v>
       </c>
       <c r="C127" t="n">
         <v>130.0736236572266</v>
@@ -3646,11 +3658,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>114.8672256469727</v>
+        <v>114.8672485351562</v>
       </c>
       <c r="C128" t="n">
         <v>134.9900360107422</v>
@@ -3675,11 +3687,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>115.6569442749023</v>
+        <v>115.6569366455078</v>
       </c>
       <c r="C129" t="n">
         <v>135.9180908203125</v>
@@ -3704,11 +3716,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>117.7384414672852</v>
+        <v>117.7384948730469</v>
       </c>
       <c r="C130" t="n">
         <v>137.8508911132812</v>
@@ -3733,11 +3745,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>109.9954071044922</v>
+        <v>109.9953842163086</v>
       </c>
       <c r="C131" t="n">
         <v>128.7850952148438</v>
@@ -3762,11 +3774,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>110.7749099731445</v>
+        <v>110.7749176025391</v>
       </c>
       <c r="C132" t="n">
         <v>129.6977996826172</v>
@@ -3791,7 +3803,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3820,11 +3832,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>116.6569900512695</v>
+        <v>116.6569747924805</v>
       </c>
       <c r="C134" t="n">
         <v>135.9794464111328</v>
@@ -3849,11 +3861,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>120.4470367431641</v>
+        <v>120.4470443725586</v>
       </c>
       <c r="C135" t="n">
         <v>140.3972930908203</v>
@@ -3878,11 +3890,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>121.1846618652344</v>
+        <v>121.1846389770508</v>
       </c>
       <c r="C136" t="n">
         <v>140.6964263916016</v>
@@ -3907,11 +3919,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>123.5166244506836</v>
+        <v>123.5166168212891</v>
       </c>
       <c r="C137" t="n">
         <v>143.4039001464844</v>
@@ -3936,11 +3948,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>125.0095901489258</v>
+        <v>125.0096054077148</v>
       </c>
       <c r="C138" t="n">
         <v>145.1372985839844</v>
@@ -3965,7 +3977,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3994,11 +4006,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>133.5575256347656</v>
+        <v>133.5574951171875</v>
       </c>
       <c r="C140" t="n">
         <v>154.4715423583984</v>
@@ -4023,11 +4035,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>132.2577056884766</v>
+        <v>132.2576599121094</v>
       </c>
       <c r="C141" t="n">
         <v>152.9682464599609</v>
@@ -4052,7 +4064,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4081,11 +4093,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>138.8874816894531</v>
+        <v>138.8874359130859</v>
       </c>
       <c r="C143" t="n">
         <v>160.0475463867188</v>
@@ -4110,11 +4122,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>151.8929595947266</v>
+        <v>151.8929901123047</v>
       </c>
       <c r="C144" t="n">
         <v>175.0345153808594</v>
@@ -4139,11 +4151,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>142.9647216796875</v>
+        <v>142.9647674560547</v>
       </c>
       <c r="C145" t="n">
         <v>164.1816253662109</v>
@@ -4168,11 +4180,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>162.2528381347656</v>
+        <v>162.2528991699219</v>
       </c>
       <c r="C146" t="n">
         <v>186.3322601318359</v>
@@ -4197,11 +4209,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>148.2809906005859</v>
+        <v>148.2810211181641</v>
       </c>
       <c r="C147" t="n">
         <v>170.2868499755859</v>
@@ -4226,11 +4238,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>145.2250518798828</v>
+        <v>145.2250823974609</v>
       </c>
       <c r="C148" t="n">
         <v>166.2064666748047</v>
@@ -4255,7 +4267,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4284,11 +4296,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>148.5021514892578</v>
+        <v>148.5021667480469</v>
       </c>
       <c r="C150" t="n">
         <v>169.9570465087891</v>
@@ -4311,11 +4323,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>161.0666046142578</v>
+        <v>161.0665740966797</v>
       </c>
       <c r="C151" t="n">
         <v>183.7398376464844</v>
@@ -4338,11 +4350,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>168.3346099853516</v>
+        <v>168.3346405029297</v>
       </c>
       <c r="C152" t="n">
         <v>192.0309906005859</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>176.066650390625</v>
+        <v>176.0666198730469</v>
       </c>
       <c r="C153" t="n">
         <v>200.8513641357422</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>175.9941253662109</v>
+        <v>175.9941101074219</v>
       </c>
       <c r="C154" t="n">
         <v>200.18408203125</v>
@@ -4423,7 +4435,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>170.4310913085938</v>
+        <v>170.4310455322266</v>
       </c>
       <c r="C156" t="n">
         <v>193.8564147949219</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>152.4213714599609</v>
+        <v>152.4213562011719</v>
       </c>
       <c r="C157" t="n">
         <v>172.8179168701172</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>168.7512054443359</v>
+        <v>168.7512359619141</v>
       </c>
       <c r="C158" t="n">
         <v>191.3330230712891</v>
@@ -4539,7 +4551,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>169.4588470458984</v>
+        <v>169.4588012695312</v>
       </c>
       <c r="C160" t="n">
         <v>191.5401153564453</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>163.3584594726562</v>
+        <v>163.3584442138672</v>
       </c>
       <c r="C161" t="n">
         <v>184.6448822021484</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>158.4049530029297</v>
+        <v>158.4049377441406</v>
       </c>
       <c r="C162" t="n">
         <v>179.0458679199219</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>171.5578308105469</v>
+        <v>171.5578155517578</v>
       </c>
       <c r="C163" t="n">
         <v>193.2888488769531</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>172.0956115722656</v>
+        <v>172.0955963134766</v>
       </c>
       <c r="C164" t="n">
         <v>193.894775390625</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>172.8580932617188</v>
+        <v>172.8580627441406</v>
       </c>
       <c r="C165" t="n">
         <v>194.7537994384766</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>172.7190399169922</v>
+        <v>172.7190551757812</v>
       </c>
       <c r="C166" t="n">
         <v>194.0174865722656</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>174.7947845458984</v>
+        <v>174.7947540283203</v>
       </c>
       <c r="C167" t="n">
         <v>196.3491363525391</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>176.5017700195312</v>
+        <v>176.5017242431641</v>
       </c>
       <c r="C168" t="n">
         <v>198.2666015625</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>186.2633666992188</v>
+        <v>186.2634124755859</v>
       </c>
       <c r="C169" t="n">
         <v>208.5979461669922</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>188.4618377685547</v>
+        <v>188.4618682861328</v>
       </c>
       <c r="C170" t="n">
         <v>211.0599822998047</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>162.8751678466797</v>
+        <v>162.8751373291016</v>
       </c>
       <c r="C171" t="n">
         <v>182.4052734375</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>157.8836517333984</v>
+        <v>157.8836059570312</v>
       </c>
       <c r="C172" t="n">
         <v>176.2310180664062</v>
@@ -4945,7 +4957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4974,7 +4986,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>164.9498596191406</v>
+        <v>164.9498291015625</v>
       </c>
       <c r="C175" t="n">
         <v>183.5174102783203</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>193.9524688720703</v>
+        <v>193.9524383544922</v>
       </c>
       <c r="C176" t="n">
         <v>215.7846374511719</v>
@@ -5061,7 +5073,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>160.9499359130859</v>
+        <v>160.9499816894531</v>
       </c>
       <c r="C178" t="n">
         <v>178.4629516601562</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>173.6828460693359</v>
+        <v>173.682861328125</v>
       </c>
       <c r="C181" t="n">
         <v>191.9159393310547</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>181.7138214111328</v>
+        <v>181.7138061523438</v>
       </c>
       <c r="C182" t="n">
         <v>200.7899932861328</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>167.3871459960938</v>
+        <v>167.3871765136719</v>
       </c>
       <c r="C183" t="n">
         <v>184.9593505859375</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>169.3465270996094</v>
+        <v>169.3465423583984</v>
       </c>
       <c r="C184" t="n">
         <v>186.4933319091797</v>
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>173.2885589599609</v>
+        <v>173.2885437011719</v>
       </c>
       <c r="C185" t="n">
         <v>190.8344879150391</v>
@@ -5322,7 +5334,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5351,7 +5363,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>178.7413482666016</v>
+        <v>178.7413330078125</v>
       </c>
       <c r="C188" t="n">
         <v>196.1573791503906</v>
@@ -5409,7 +5421,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>167.9880676269531</v>
+        <v>167.9880523681641</v>
       </c>
       <c r="C191" t="n">
         <v>183.7628479003906</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>166.2702484130859</v>
+        <v>166.270263671875</v>
       </c>
       <c r="C192" t="n">
         <v>181.8837280273438</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>176.9493865966797</v>
+        <v>176.9493713378906</v>
       </c>
       <c r="C193" t="n">
         <v>192.8823394775391</v>
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>190.8813171386719</v>
+        <v>190.8812866210938</v>
       </c>
       <c r="C195" t="n">
         <v>208.0687255859375</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>187.7823028564453</v>
+        <v>187.7823181152344</v>
       </c>
       <c r="C196" t="n">
         <v>204.0190277099609</v>
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,7 +5682,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>178.9921875</v>
+        <v>178.9922027587891</v>
       </c>
       <c r="C199" t="n">
         <v>193.8128967285156</v>
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>177.3804016113281</v>
+        <v>177.3803863525391</v>
       </c>
       <c r="C200" t="n">
         <v>192.0676116943359</v>
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>162.3302612304688</v>
+        <v>162.3302459716797</v>
       </c>
       <c r="C202" t="n">
         <v>175.1808166503906</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>171.9026336669922</v>
+        <v>171.9026184082031</v>
       </c>
       <c r="C203" t="n">
         <v>185.5110015869141</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>181.6426391601562</v>
+        <v>181.6426086425781</v>
       </c>
       <c r="C204" t="n">
         <v>196.0220184326172</v>
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>185.9424591064453</v>
+        <v>185.9424285888672</v>
       </c>
       <c r="C205" t="n">
         <v>199.92138671875</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>184.4215240478516</v>
+        <v>184.4215393066406</v>
       </c>
       <c r="C206" t="n">
         <v>198.2861633300781</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>171.5013580322266</v>
+        <v>171.5013427734375</v>
       </c>
       <c r="C207" t="n">
         <v>184.3946533203125</v>
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>177.4598083496094</v>
+        <v>177.4597778320312</v>
       </c>
       <c r="C210" t="n">
         <v>190.0628967285156</v>
@@ -6047,7 +6059,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>191.1088562011719</v>
+        <v>191.1088409423828</v>
       </c>
       <c r="C214" t="n">
         <v>203.2468566894531</v>
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>186.8583679199219</v>
+        <v>186.8583984375</v>
       </c>
       <c r="C215" t="n">
         <v>198.7264099121094</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>174.5874481201172</v>
+        <v>174.5874328613281</v>
       </c>
       <c r="C216" t="n">
         <v>185.6761016845703</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>180.9788818359375</v>
+        <v>180.9788970947266</v>
       </c>
       <c r="C217" t="n">
         <v>191.6902465820312</v>
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>174.8332214355469</v>
+        <v>174.8332061767578</v>
       </c>
       <c r="C219" t="n">
         <v>185.1808166503906</v>
@@ -6308,7 +6320,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6337,11 +6349,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>174.8330535888672</v>
+        <v>174.8330383300781</v>
       </c>
       <c r="C221" t="n">
         <v>184.4339599609375</v>
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>180.3593292236328</v>
+        <v>180.3593444824219</v>
       </c>
       <c r="C224" t="n">
         <v>189.5125732421875</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>181.369384765625</v>
+        <v>181.3694000244141</v>
       </c>
       <c r="C225" t="n">
         <v>190.5738983154297</v>
@@ -6482,7 +6494,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>175.4868774414062</v>
+        <v>175.4868621826172</v>
       </c>
       <c r="C227" t="n">
         <v>183.6399383544922</v>
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>166.7046356201172</v>
+        <v>166.7046508789062</v>
       </c>
       <c r="C228" t="n">
         <v>174.4496917724609</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>171.2478637695312</v>
+        <v>171.2478485107422</v>
       </c>
       <c r="C229" t="n">
         <v>178.3569183349609</v>
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,11 +6639,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>170.2363739013672</v>
+        <v>170.2364044189453</v>
       </c>
       <c r="C231" t="n">
         <v>177.3034515380859</v>
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>173.6878509521484</v>
+        <v>173.6878662109375</v>
       </c>
       <c r="C232" t="n">
         <v>180.07861328125</v>
@@ -6685,11 +6697,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>157.0288238525391</v>
+        <v>157.02880859375</v>
       </c>
       <c r="C233" t="n">
         <v>162.8066101074219</v>
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>130.8687286376953</v>
+        <v>130.8687133789062</v>
       </c>
       <c r="C234" t="n">
         <v>135.6839599609375</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>131.3987731933594</v>
+        <v>131.3987884521484</v>
       </c>
       <c r="C235" t="n">
         <v>135.4166717529297</v>
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>147.2124176025391</v>
+        <v>147.21240234375</v>
       </c>
       <c r="C237" t="n">
         <v>151.7138366699219</v>
@@ -6830,7 +6842,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6859,11 +6871,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>137.0676574707031</v>
+        <v>137.0676422119141</v>
       </c>
       <c r="C239" t="n">
         <v>140.4952850341797</v>
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>182.5200042724609</v>
+        <v>179.2299957275391</v>
       </c>
       <c r="C250" t="n">
-        <v>182.5200042724609</v>
+        <v>179.2299957275391</v>
       </c>
       <c r="D250" t="n">
-        <v>29677500</v>
+        <v>31082300</v>
       </c>
       <c r="E250" t="n">
         <v>2.657798742138365</v>
       </c>
       <c r="F250" t="n">
-        <v>68.67337296036652</v>
+        <v>67.43550325535082</v>
       </c>
       <c r="G250" t="n">
         <v>272386800</v>
       </c>
       <c r="H250" t="n">
-        <v>49716039899.76196</v>
+        <v>48819885000.23804</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1089535175713361</v>
+        <v>0.1141108893676199</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40217</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40217</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7624,7 +7636,7 @@
       <c r="I9" t="n">
         <v>4.210768522779568</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="K9" t="n">
@@ -7637,13 +7649,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7670,7 +7682,7 @@
       <c r="I10" t="n">
         <v>4.256787850897378</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="K10" t="n">
@@ -7683,13 +7695,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7716,7 +7728,7 @@
       <c r="I11" t="n">
         <v>4.364166283172267</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K11" t="n">
@@ -7729,13 +7741,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="I12" t="n">
         <v>4.548243595643504</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="K12" t="n">
@@ -7775,13 +7787,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7808,7 +7820,7 @@
       <c r="I13" t="n">
         <v>4.310477067034822</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="K13" t="n">
@@ -7821,13 +7833,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7854,7 +7866,7 @@
       <c r="I14" t="n">
         <v>4.195428746740298</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="K14" t="n">
@@ -7867,13 +7879,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7900,7 +7912,7 @@
       <c r="I15" t="n">
         <v>4.203098634759932</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K15" t="n">
@@ -7913,13 +7925,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="I16" t="n">
         <v>4.249117962877742</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K16" t="n">
@@ -7959,13 +7971,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7992,7 +8004,7 @@
       <c r="I17" t="n">
         <v>4.287467402975917</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="K17" t="n">
@@ -8005,13 +8017,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8038,7 +8050,7 @@
       <c r="I18" t="n">
         <v>5.760085902745821</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="K18" t="n">
@@ -8051,13 +8063,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41268</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8084,7 +8096,7 @@
       <c r="I19" t="n">
         <v>5.76008590274582</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K19" t="n">
@@ -8097,13 +8109,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8130,7 +8142,7 @@
       <c r="I20" t="n">
         <v>5.706396686608376</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="K20" t="n">
@@ -8143,13 +8155,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8176,7 +8188,7 @@
       <c r="I21" t="n">
         <v>4.97775732474306</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="K21" t="n">
@@ -8189,13 +8201,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="I22" t="n">
         <v>3.627857033287315</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="K22" t="n">
@@ -8235,13 +8247,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8268,7 +8280,7 @@
       <c r="I23" t="n">
         <v>3.673876361405124</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="K23" t="n">
@@ -8281,13 +8293,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8314,7 +8326,7 @@
       <c r="I24" t="n">
         <v>3.773584905660378</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="K24" t="n">
@@ -8327,13 +8339,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8360,7 +8372,7 @@
       <c r="I25" t="n">
         <v>4.594262923761313</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="K25" t="n">
@@ -8373,13 +8385,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8406,7 +8418,7 @@
       <c r="I26" t="n">
         <v>4.46387482742752</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="K26" t="n">
@@ -8419,13 +8431,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8452,7 +8464,7 @@
       <c r="I27" t="n">
         <v>4.180088970701028</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="K27" t="n">
@@ -8465,13 +8477,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8498,7 +8510,7 @@
       <c r="I28" t="n">
         <v>3.13698420003068</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K28" t="n">
@@ -8511,13 +8523,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8544,7 +8556,7 @@
       <c r="I29" t="n">
         <v>2.615431814695506</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="K29" t="n">
@@ -8557,13 +8569,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8590,7 +8602,7 @@
       <c r="I30" t="n">
         <v>2.508053382420617</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="K30" t="n">
@@ -8603,13 +8615,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8636,7 +8648,7 @@
       <c r="I31" t="n">
         <v>2.876208007363093</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K31" t="n">
@@ -8649,13 +8661,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8682,7 +8694,7 @@
       <c r="I32" t="n">
         <v>4.034361098327965</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K32" t="n">
@@ -8695,13 +8707,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8728,7 +8740,7 @@
       <c r="I33" t="n">
         <v>3.459119496855346</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="K33" t="n">
@@ -8741,13 +8753,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42768</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8774,7 +8786,7 @@
       <c r="I34" t="n">
         <v>4.624942475839854</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42768</v>
       </c>
       <c r="K34" t="n">
@@ -8787,13 +8799,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8820,7 +8832,7 @@
       <c r="I35" t="n">
         <v>4.640282251879123</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K35" t="n">
@@ -8833,13 +8845,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8866,7 +8878,7 @@
       <c r="I36" t="n">
         <v>2.68446080687222</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K36" t="n">
@@ -8879,13 +8891,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8912,7 +8924,7 @@
       <c r="I37" t="n">
         <v>3.566497929130235</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="K37" t="n">
@@ -8925,13 +8937,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8958,7 +8970,7 @@
       <c r="I38" t="n">
         <v>1.004755330572174</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="K38" t="n">
@@ -8971,13 +8983,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9004,7 +9016,7 @@
       <c r="I39" t="n">
         <v>-0.3528148489032061</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K39" t="n">
@@ -9017,13 +9029,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9050,7 +9062,7 @@
       <c r="I40" t="n">
         <v>1.7794140205553</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -9063,13 +9075,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9096,7 +9108,7 @@
       <c r="I41" t="n">
         <v>0.3374750728639361</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="K41" t="n">
@@ -9109,13 +9121,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="I42" t="n">
         <v>2.492713606381347</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="K42" t="n">
@@ -9155,13 +9167,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9188,7 +9200,7 @@
       <c r="I43" t="n">
         <v>2.584752262616966</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K43" t="n">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I44" t="n">
         <v>2.185918085595951</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K44" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I45" t="n">
         <v>3.021935879736156</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="K45" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I46" t="n">
         <v>2.116889093419236</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K46" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I47" t="n">
         <v>2.577082374597331</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I48" t="n">
         <v>2.162908421537046</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K48" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I49" t="n">
         <v>2.093879429360332</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="K49" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I50" t="n">
         <v>3.99601165822979</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="K50" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I51" t="n">
         <v>4.310477067034822</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K51" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I52" t="n">
         <v>4.88571866850744</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K52" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I53" t="n">
         <v>5.253873293449916</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="K53" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I54" t="n">
         <v>4.433195275348981</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K54" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I55" t="n">
         <v>4.891471084522166</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K55" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I56" t="n">
         <v>4.499923301119804</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I57" t="n">
         <v>4.622641509433962</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="K57" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I58" t="n">
         <v>4.210385028378586</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K58" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I59" t="n">
         <v>4.233969934038964</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K59" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I60" t="n">
         <v>4.375479368001228</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K60" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I61" t="n">
         <v>3.883647798742139</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="K61" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I62" t="n">
         <v>3.30188679245283</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="K62" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I63" t="n">
         <v>3.553459119496856</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I64" t="n">
         <v>3.805031446540881</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I65" t="n">
         <v>4.60691823899371</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="K65" t="n">
@@ -10213,13 +10225,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10246,7 +10258,7 @@
       <c r="I66" t="n">
         <v>4.669811320754717</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="K66" t="n">
@@ -10259,13 +10271,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10292,7 +10304,7 @@
       <c r="I67" t="n">
         <v>4.056603773584905</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K67" t="n">
@@ -10305,13 +10317,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10338,7 +10350,7 @@
       <c r="I68" t="n">
         <v>4.308176100628931</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K68" t="n">
@@ -10351,13 +10363,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10384,7 +10396,7 @@
       <c r="I69" t="n">
         <v>4.575471698113208</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="K69" t="n">
@@ -10397,13 +10409,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10430,7 +10442,7 @@
       <c r="I70" t="n">
         <v>4.811320754716982</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="K70" t="n">
@@ -10443,13 +10455,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10476,7 +10488,7 @@
       <c r="I71" t="n">
         <v>2.860125786163522</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K71" t="n">
@@ -10489,13 +10501,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="I72" t="n">
         <v>2.657798742138365</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K72" t="n">
@@ -10559,52 +10571,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10633,10 +10645,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40142</v>
       </c>
       <c r="C3" t="n">
@@ -10665,10 +10677,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40217</v>
       </c>
       <c r="C4" t="n">
@@ -10697,10 +10709,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10729,10 +10741,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40394</v>
       </c>
       <c r="C6" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40506</v>
       </c>
       <c r="C7" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40582</v>
       </c>
       <c r="C8" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="C10" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="C11" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="C12" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="C15" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41312</v>
       </c>
       <c r="C16" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C17" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41491</v>
       </c>
       <c r="C18" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="C19" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="C20" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41764</v>
       </c>
       <c r="C21" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41855</v>
       </c>
       <c r="C22" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41969</v>
       </c>
       <c r="C23" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="C24" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="C25" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C26" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42333</v>
       </c>
       <c r="C27" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="C28" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C29" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C30" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42697</v>
       </c>
       <c r="C31" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42768</v>
       </c>
       <c r="C32" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43061</v>
       </c>
       <c r="C35" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="C36" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C37" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C38" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43425</v>
       </c>
       <c r="C39" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43501</v>
       </c>
       <c r="C40" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C41" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43796</v>
       </c>
       <c r="C43" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C44" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C45" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44160</v>
       </c>
       <c r="C47" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44231</v>
       </c>
       <c r="C48" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44524</v>
       </c>
       <c r="C51" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C52" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C53" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="C55" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C56" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C57" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="C59" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="C60" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45623</v>
       </c>
       <c r="C63" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C64" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C66" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="C67" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46062</v>
       </c>
       <c r="C68" t="n">
@@ -12745,10 +12757,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C69" t="n">
@@ -12777,10 +12789,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C70" t="n">
@@ -12827,12 +12839,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BDX.xlsx
+++ b/salidas/empresas/BDX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>34.90283966064453</v>
+        <v>34.90282821655273</v>
       </c>
       <c r="C2" t="n">
         <v>49.70087432861328</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>34.39115142822266</v>
+        <v>34.39113998413086</v>
       </c>
       <c r="C3" t="n">
         <v>48.97223663330078</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.28261566162109</v>
+        <v>33.28261184692383</v>
       </c>
       <c r="C4" t="n">
         <v>47.23117065429688</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>34.07171630859375</v>
+        <v>34.07171249389648</v>
       </c>
       <c r="C5" t="n">
         <v>48.35097503662109</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>32.66106414794922</v>
+        <v>32.66107559204102</v>
       </c>
       <c r="C6" t="n">
         <v>46.3491325378418</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.15693664550781</v>
+        <v>33.15695190429688</v>
       </c>
       <c r="C7" t="n">
         <v>46.88602447509766</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.75504684448242</v>
+        <v>35.75506973266602</v>
       </c>
       <c r="C8" t="n">
         <v>50.55990219116211</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>37.80532455444336</v>
+        <v>37.80534744262695</v>
       </c>
       <c r="C9" t="n">
         <v>53.4591178894043</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>38.44999694824219</v>
+        <v>38.44997406005859</v>
       </c>
       <c r="C10" t="n">
         <v>54.20309829711914</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>38.10178756713867</v>
+        <v>38.10176086425781</v>
       </c>
       <c r="C11" t="n">
         <v>53.71222686767578</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>39.02127075195312</v>
+        <v>39.02125549316406</v>
       </c>
       <c r="C12" t="n">
         <v>55.00843811035156</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>38.29553604125977</v>
+        <v>38.2955322265625</v>
       </c>
       <c r="C13" t="n">
         <v>53.80426406860352</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>42.00226211547852</v>
+        <v>42.00224685668945</v>
       </c>
       <c r="C14" t="n">
         <v>59.01211929321289</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>41.46181488037109</v>
+        <v>41.46182250976562</v>
       </c>
       <c r="C15" t="n">
         <v>58.25279998779297</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.1134147644043</v>
+        <v>42.11341094970703</v>
       </c>
       <c r="C16" t="n">
         <v>58.97377014160156</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>41.76288986206055</v>
+        <v>41.76289367675781</v>
       </c>
       <c r="C18" t="n">
         <v>58.48289489746094</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>40.93716049194336</v>
+        <v>40.93717956542969</v>
       </c>
       <c r="C19" t="n">
         <v>57.14066696166992</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.95922470092773</v>
+        <v>41.959228515625</v>
       </c>
       <c r="C20" t="n">
         <v>58.56726455688477</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>42.27793121337891</v>
+        <v>42.27791976928711</v>
       </c>
       <c r="C21" t="n">
         <v>59.01211929321289</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>45.22970199584961</v>
+        <v>45.22970581054688</v>
       </c>
       <c r="C22" t="n">
         <v>62.93143081665039</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.00695419311523</v>
+        <v>46.0069580078125</v>
       </c>
       <c r="C23" t="n">
         <v>64.01288604736328</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>45.60454940795898</v>
+        <v>45.60455322265625</v>
       </c>
       <c r="C24" t="n">
         <v>63.45298385620117</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>46.23249053955078</v>
+        <v>46.23246765136719</v>
       </c>
       <c r="C25" t="n">
         <v>64.10492706298828</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>47.81449508666992</v>
+        <v>47.81448745727539</v>
       </c>
       <c r="C26" t="n">
         <v>66.29851531982422</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.01604080200195</v>
+        <v>50.01603698730469</v>
       </c>
       <c r="C27" t="n">
         <v>69.35112762451172</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>47.64012908935547</v>
+        <v>47.6401252746582</v>
       </c>
       <c r="C28" t="n">
         <v>65.84598541259766</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>49.61009979248047</v>
+        <v>49.61008453369141</v>
       </c>
       <c r="C29" t="n">
         <v>68.56880187988281</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>46.86322402954102</v>
+        <v>46.86323165893555</v>
       </c>
       <c r="C30" t="n">
         <v>64.77220153808594</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>45.26858139038086</v>
+        <v>45.26856994628906</v>
       </c>
       <c r="C31" t="n">
         <v>62.3561897277832</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>47.27867126464844</v>
+        <v>47.27865600585938</v>
       </c>
       <c r="C32" t="n">
         <v>65.12501525878906</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>48.65398406982422</v>
+        <v>48.65398788452148</v>
       </c>
       <c r="C33" t="n">
         <v>67.01948547363281</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>44.83847427368164</v>
+        <v>44.83847808837891</v>
       </c>
       <c r="C34" t="n">
         <v>61.55852127075195</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>38.77136993408203</v>
+        <v>38.77134704589844</v>
       </c>
       <c r="C35" t="n">
         <v>53.22902297973633</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>35.49200439453125</v>
+        <v>35.49201583862305</v>
       </c>
       <c r="C36" t="n">
         <v>48.72679901123047</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>38.40851211547852</v>
+        <v>38.40851974487305</v>
       </c>
       <c r="C37" t="n">
         <v>52.45436477661133</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>40.81220245361328</v>
+        <v>40.81223297119141</v>
       </c>
       <c r="C38" t="n">
         <v>55.73707580566406</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>34.75805282592773</v>
+        <v>34.75806427001953</v>
       </c>
       <c r="C39" t="n">
         <v>47.46893692016602</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>37.95853424072266</v>
+        <v>37.95853042602539</v>
       </c>
       <c r="C40" t="n">
         <v>51.57232666015625</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>34.14237594604492</v>
+        <v>34.14237976074219</v>
       </c>
       <c r="C41" t="n">
         <v>46.38748168945312</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>38.20693969726562</v>
+        <v>38.20693206787109</v>
       </c>
       <c r="C42" t="n">
         <v>51.9098014831543</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>40.45386505126953</v>
+        <v>40.45387268066406</v>
       </c>
       <c r="C43" t="n">
         <v>54.6939697265625</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>36.95932769775391</v>
+        <v>36.95934295654297</v>
       </c>
       <c r="C44" t="n">
         <v>49.96931838989258</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>39.49514770507812</v>
+        <v>39.49513626098633</v>
       </c>
       <c r="C45" t="n">
         <v>53.39775848388672</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>39.75905227661133</v>
+        <v>39.75904083251953</v>
       </c>
       <c r="C46" t="n">
         <v>53.49747085571289</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>38.96671676635742</v>
+        <v>38.96671295166016</v>
       </c>
       <c r="C47" t="n">
         <v>52.43135452270508</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.63766479492188</v>
+        <v>42.63766860961914</v>
       </c>
       <c r="C48" t="n">
         <v>57.37076187133789</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>45.1690559387207</v>
+        <v>45.16904830932617</v>
       </c>
       <c r="C49" t="n">
         <v>60.48473739624023</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>43.17005920410156</v>
+        <v>43.17006683349609</v>
       </c>
       <c r="C50" t="n">
         <v>57.80794525146484</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>44.60200881958008</v>
+        <v>44.60200119018555</v>
       </c>
       <c r="C51" t="n">
         <v>59.72541809082031</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>45.3078727722168</v>
+        <v>45.30786895751953</v>
       </c>
       <c r="C52" t="n">
         <v>60.38502883911133</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>43.94973373413086</v>
+        <v>43.94972610473633</v>
       </c>
       <c r="C53" t="n">
         <v>58.57493591308594</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.03203201293945</v>
+        <v>41.03201675415039</v>
       </c>
       <c r="C54" t="n">
         <v>54.68630218505859</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>39.12078475952148</v>
+        <v>39.12080001831055</v>
       </c>
       <c r="C55" t="n">
         <v>51.86378479003906</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>39.80345153808594</v>
+        <v>39.80347061157227</v>
       </c>
       <c r="C56" t="n">
         <v>52.76882934570312</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>39.4505615234375</v>
+        <v>39.4505500793457</v>
       </c>
       <c r="C57" t="n">
         <v>52.30096435546875</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>43.09550476074219</v>
+        <v>43.09552383422852</v>
       </c>
       <c r="C58" t="n">
         <v>56.83386993408203</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>43.92136383056641</v>
+        <v>43.92136001586914</v>
       </c>
       <c r="C59" t="n">
         <v>57.92299270629883</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>45.32297897338867</v>
+        <v>45.32300186157227</v>
       </c>
       <c r="C60" t="n">
         <v>59.77143859863281</v>
@@ -1748,7 +1748,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>48.48681259155273</v>
+        <v>48.4868278503418</v>
       </c>
       <c r="C62" t="n">
         <v>63.62171936035156</v>
@@ -1777,7 +1777,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>46.76246643066406</v>
+        <v>46.762451171875</v>
       </c>
       <c r="C63" t="n">
         <v>61.35910415649414</v>
@@ -1806,7 +1806,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>46.78188323974609</v>
+        <v>46.78186416625977</v>
       </c>
       <c r="C64" t="n">
         <v>61.06764984130859</v>
@@ -1864,7 +1864,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>51.44127655029297</v>
+        <v>51.44125747680664</v>
       </c>
       <c r="C66" t="n">
         <v>67.14987182617188</v>
@@ -1893,7 +1893,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>50.87521743774414</v>
+        <v>50.87522506713867</v>
       </c>
       <c r="C67" t="n">
         <v>66.09142303466797</v>
@@ -1922,7 +1922,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>49.36378860473633</v>
+        <v>49.36377334594727</v>
       </c>
       <c r="C68" t="n">
         <v>64.12793731689453</v>
@@ -1951,7 +1951,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>48.04718399047852</v>
+        <v>48.04716491699219</v>
       </c>
       <c r="C69" t="n">
         <v>62.41754913330078</v>
@@ -1980,7 +1980,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>43.5159797668457</v>
+        <v>43.51600646972656</v>
       </c>
       <c r="C70" t="n">
         <v>56.23561859130859</v>
@@ -2038,7 +2038,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>43.78900909423828</v>
+        <v>43.78900146484375</v>
       </c>
       <c r="C72" t="n">
         <v>56.58843231201172</v>
@@ -2067,7 +2067,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>44.61777877807617</v>
+        <v>44.6177978515625</v>
       </c>
       <c r="C73" t="n">
         <v>57.30940246582031</v>
@@ -2096,7 +2096,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.82120513916016</v>
+        <v>46.82122039794922</v>
       </c>
       <c r="C74" t="n">
         <v>60.13959121704102</v>
@@ -2125,7 +2125,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>45.51349258422852</v>
+        <v>45.51348495483398</v>
       </c>
       <c r="C75" t="n">
         <v>58.45988464355469</v>
@@ -2154,7 +2154,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.6456298828125</v>
+        <v>46.6456184387207</v>
       </c>
       <c r="C76" t="n">
         <v>59.55667877197266</v>
@@ -2212,7 +2212,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.93038940429688</v>
+        <v>43.93039321899414</v>
       </c>
       <c r="C78" t="n">
         <v>56.08988952636719</v>
@@ -2241,7 +2241,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>45.18366622924805</v>
+        <v>45.18365097045898</v>
       </c>
       <c r="C79" t="n">
         <v>57.33241271972656</v>
@@ -2270,7 +2270,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>45.76394271850586</v>
+        <v>45.76393127441406</v>
       </c>
       <c r="C80" t="n">
         <v>58.06872177124023</v>
@@ -2299,7 +2299,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>45.92714309692383</v>
+        <v>45.92714691162109</v>
       </c>
       <c r="C81" t="n">
         <v>58.27581024169922</v>
@@ -2328,7 +2328,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>47.76735305786133</v>
+        <v>47.76733779907227</v>
       </c>
       <c r="C82" t="n">
         <v>60.254638671875</v>
@@ -2357,7 +2357,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>46.01620483398438</v>
+        <v>46.01619338989258</v>
       </c>
       <c r="C83" t="n">
         <v>58.04571151733398</v>
@@ -2386,7 +2386,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>46.6181526184082</v>
+        <v>46.61816024780273</v>
       </c>
       <c r="C84" t="n">
         <v>58.80503082275391</v>
@@ -2415,7 +2415,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>47.84842300415039</v>
+        <v>47.84842681884766</v>
       </c>
       <c r="C85" t="n">
         <v>59.97085571289062</v>
@@ -2444,7 +2444,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>51.42832565307617</v>
+        <v>51.42832946777344</v>
       </c>
       <c r="C86" t="n">
         <v>64.45774078369141</v>
@@ -2502,7 +2502,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.83513259887695</v>
+        <v>58.83512496948242</v>
       </c>
       <c r="C88" t="n">
         <v>73.33180236816406</v>
@@ -2531,7 +2531,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>58.02898406982422</v>
+        <v>58.02899932861328</v>
       </c>
       <c r="C89" t="n">
         <v>72.32704162597656</v>
@@ -2560,7 +2560,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>60.68738555908203</v>
+        <v>60.68739318847656</v>
       </c>
       <c r="C90" t="n">
         <v>75.64043426513672</v>
@@ -2589,7 +2589,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>61.12417602539062</v>
+        <v>61.12420272827148</v>
       </c>
       <c r="C91" t="n">
         <v>75.80150604248047</v>
@@ -2618,7 +2618,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>64.14855194091797</v>
+        <v>64.14857482910156</v>
       </c>
       <c r="C92" t="n">
         <v>79.55207824707031</v>
@@ -2647,7 +2647,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>60.22737121582031</v>
+        <v>60.22739791870117</v>
       </c>
       <c r="C93" t="n">
         <v>74.68936920166016</v>
@@ -2676,7 +2676,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>62.17192840576172</v>
+        <v>62.17191314697266</v>
       </c>
       <c r="C94" t="n">
         <v>76.71421813964844</v>
@@ -2705,7 +2705,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>65.3482666015625</v>
+        <v>65.34825134277344</v>
       </c>
       <c r="C95" t="n">
         <v>80.63352966308594</v>
@@ -2734,7 +2734,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>67.49900054931641</v>
+        <v>67.49900817871094</v>
       </c>
       <c r="C96" t="n">
         <v>83.28731536865234</v>
@@ -2763,7 +2763,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>69.03164672851562</v>
+        <v>69.03165435791016</v>
       </c>
       <c r="C97" t="n">
         <v>84.74459075927734</v>
@@ -2792,7 +2792,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>67.55088043212891</v>
+        <v>67.5509033203125</v>
       </c>
       <c r="C98" t="n">
         <v>82.92682647705078</v>
@@ -2821,7 +2821,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>71.98682403564453</v>
+        <v>71.98683166503906</v>
       </c>
       <c r="C99" t="n">
         <v>88.37245178222656</v>
@@ -2879,7 +2879,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>70.95111846923828</v>
+        <v>70.95109558105469</v>
       </c>
       <c r="C101" t="n">
         <v>86.69274139404297</v>
@@ -2937,7 +2937,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>74.60020446777344</v>
+        <v>74.6002197265625</v>
       </c>
       <c r="C103" t="n">
         <v>90.73477172851562</v>
@@ -2995,7 +2995,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>73.88762664794922</v>
+        <v>73.88761901855469</v>
       </c>
       <c r="C105" t="n">
         <v>89.86808013916016</v>
@@ -3024,7 +3024,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>72.10637664794922</v>
+        <v>72.10636138916016</v>
       </c>
       <c r="C106" t="n">
         <v>87.29099273681641</v>
@@ -3053,7 +3053,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>81.54016876220703</v>
+        <v>81.54022979736328</v>
       </c>
       <c r="C107" t="n">
         <v>98.71145629882812</v>
@@ -3111,7 +3111,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>88.54913330078125</v>
+        <v>88.54914093017578</v>
       </c>
       <c r="C109" t="n">
         <v>106.7341613769531</v>
@@ -3140,7 +3140,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>87.86190795898438</v>
+        <v>87.86195373535156</v>
       </c>
       <c r="C110" t="n">
         <v>105.9058151245117</v>
@@ -3169,7 +3169,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>93.35966491699219</v>
+        <v>93.35964965820312</v>
       </c>
       <c r="C111" t="n">
         <v>112.532600402832</v>
@@ -3198,7 +3198,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>91.73616027832031</v>
+        <v>91.73617553710938</v>
       </c>
       <c r="C112" t="n">
         <v>110.1319198608398</v>
@@ -3227,7 +3227,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>89.99842071533203</v>
+        <v>89.99844360351562</v>
       </c>
       <c r="C113" t="n">
         <v>108.0457153320312</v>
@@ -3285,7 +3285,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>90.88573455810547</v>
+        <v>90.88569641113281</v>
       </c>
       <c r="C115" t="n">
         <v>108.6439666748047</v>
@@ -3314,7 +3314,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>97.62276458740234</v>
+        <v>97.62274169921875</v>
       </c>
       <c r="C116" t="n">
         <v>116.6973495483398</v>
@@ -3343,7 +3343,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>90.48150634765625</v>
+        <v>90.48152160644531</v>
       </c>
       <c r="C117" t="n">
         <v>108.160758972168</v>
@@ -3430,7 +3430,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>96.82920837402344</v>
+        <v>96.82921600341797</v>
       </c>
       <c r="C120" t="n">
         <v>115.2400665283203</v>
@@ -3459,7 +3459,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>99.73238372802734</v>
+        <v>99.73236846923828</v>
       </c>
       <c r="C121" t="n">
         <v>118.185302734375</v>
@@ -3488,7 +3488,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>94.0885009765625</v>
+        <v>94.08848571777344</v>
       </c>
       <c r="C122" t="n">
         <v>111.4971618652344</v>
@@ -3517,7 +3517,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>95.43476867675781</v>
+        <v>95.43476104736328</v>
       </c>
       <c r="C123" t="n">
         <v>113.0924987792969</v>
@@ -3546,7 +3546,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>98.7012939453125</v>
+        <v>98.70130920410156</v>
       </c>
       <c r="C124" t="n">
         <v>116.4442367553711</v>
@@ -3575,7 +3575,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>104.8384323120117</v>
+        <v>104.8384552001953</v>
       </c>
       <c r="C125" t="n">
         <v>123.6846160888672</v>
@@ -3604,7 +3604,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>108.2125473022461</v>
+        <v>108.2125625610352</v>
       </c>
       <c r="C126" t="n">
         <v>127.665283203125</v>
@@ -3633,7 +3633,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>110.6837005615234</v>
+        <v>110.6836929321289</v>
       </c>
       <c r="C127" t="n">
         <v>130.0736236572266</v>
@@ -3662,7 +3662,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>114.8672485351562</v>
+        <v>114.8672332763672</v>
       </c>
       <c r="C128" t="n">
         <v>134.9900360107422</v>
@@ -3691,7 +3691,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>115.6569366455078</v>
+        <v>115.6569442749023</v>
       </c>
       <c r="C129" t="n">
         <v>135.9180908203125</v>
@@ -3720,7 +3720,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>117.7384948730469</v>
+        <v>117.7384719848633</v>
       </c>
       <c r="C130" t="n">
         <v>137.8508911132812</v>
@@ -3749,7 +3749,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>109.9953842163086</v>
+        <v>109.9953765869141</v>
       </c>
       <c r="C131" t="n">
         <v>128.7850952148438</v>
@@ -3778,7 +3778,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>110.7749176025391</v>
+        <v>110.7749328613281</v>
       </c>
       <c r="C132" t="n">
         <v>129.6977996826172</v>
@@ -3807,7 +3807,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>108.9320526123047</v>
+        <v>108.9320755004883</v>
       </c>
       <c r="C133" t="n">
         <v>126.9749984741211</v>
@@ -3836,7 +3836,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>116.6569747924805</v>
+        <v>116.6569976806641</v>
       </c>
       <c r="C134" t="n">
         <v>135.9794464111328</v>
@@ -3865,7 +3865,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>120.4470443725586</v>
+        <v>120.4470596313477</v>
       </c>
       <c r="C135" t="n">
         <v>140.3972930908203</v>
@@ -3894,7 +3894,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>121.1846389770508</v>
+        <v>121.1846084594727</v>
       </c>
       <c r="C136" t="n">
         <v>140.6964263916016</v>
@@ -3923,7 +3923,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>123.5166168212891</v>
+        <v>123.5166244506836</v>
       </c>
       <c r="C137" t="n">
         <v>143.4039001464844</v>
@@ -3952,7 +3952,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>125.0096054077148</v>
+        <v>125.009651184082</v>
       </c>
       <c r="C138" t="n">
         <v>145.1372985839844</v>
@@ -3981,7 +3981,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>129.3862915039062</v>
+        <v>129.3863067626953</v>
       </c>
       <c r="C139" t="n">
         <v>149.6471862792969</v>
@@ -4010,7 +4010,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>133.5574951171875</v>
+        <v>133.5574645996094</v>
       </c>
       <c r="C140" t="n">
         <v>154.4715423583984</v>
@@ -4039,7 +4039,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>132.2576599121094</v>
+        <v>132.2577209472656</v>
       </c>
       <c r="C141" t="n">
         <v>152.9682464599609</v>
@@ -4097,7 +4097,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>138.8874359130859</v>
+        <v>138.887451171875</v>
       </c>
       <c r="C143" t="n">
         <v>160.0475463867188</v>
@@ -4126,7 +4126,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>151.8929901123047</v>
+        <v>151.8929290771484</v>
       </c>
       <c r="C144" t="n">
         <v>175.0345153808594</v>
@@ -4155,7 +4155,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>142.9647674560547</v>
+        <v>142.9646911621094</v>
       </c>
       <c r="C145" t="n">
         <v>164.1816253662109</v>
@@ -4213,7 +4213,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>148.2810211181641</v>
+        <v>148.2809600830078</v>
       </c>
       <c r="C147" t="n">
         <v>170.2868499755859</v>
@@ -4242,7 +4242,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>145.2250823974609</v>
+        <v>145.2250671386719</v>
       </c>
       <c r="C148" t="n">
         <v>166.2064666748047</v>
@@ -4271,7 +4271,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>155.3914947509766</v>
+        <v>155.3914794921875</v>
       </c>
       <c r="C149" t="n">
         <v>177.8416900634766</v>
@@ -4300,7 +4300,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>148.5021667480469</v>
+        <v>148.5021209716797</v>
       </c>
       <c r="C150" t="n">
         <v>169.9570465087891</v>
@@ -4327,7 +4327,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>161.0665740966797</v>
+        <v>161.0666046142578</v>
       </c>
       <c r="C151" t="n">
         <v>183.7398376464844</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>176.0666198730469</v>
+        <v>176.0665893554688</v>
       </c>
       <c r="C153" t="n">
         <v>200.8513641357422</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>175.9941101074219</v>
+        <v>175.9940795898438</v>
       </c>
       <c r="C154" t="n">
         <v>200.18408203125</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>155.4277496337891</v>
+        <v>155.4277038574219</v>
       </c>
       <c r="C155" t="n">
         <v>176.7909240722656</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>170.4310455322266</v>
+        <v>170.4309997558594</v>
       </c>
       <c r="C156" t="n">
         <v>193.8564147949219</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>152.4213562011719</v>
+        <v>152.4213256835938</v>
       </c>
       <c r="C157" t="n">
         <v>172.8179168701172</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>168.7512359619141</v>
+        <v>168.7512664794922</v>
       </c>
       <c r="C158" t="n">
         <v>191.3330230712891</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>168.2980041503906</v>
+        <v>168.2979888916016</v>
       </c>
       <c r="C159" t="n">
         <v>190.8191375732422</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>169.4588012695312</v>
+        <v>169.4587860107422</v>
       </c>
       <c r="C160" t="n">
         <v>191.5401153564453</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>163.3584442138672</v>
+        <v>163.3584747314453</v>
       </c>
       <c r="C161" t="n">
         <v>184.6448822021484</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>158.4049377441406</v>
+        <v>158.4049530029297</v>
       </c>
       <c r="C162" t="n">
         <v>179.0458679199219</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>172.0955963134766</v>
+        <v>172.0956115722656</v>
       </c>
       <c r="C164" t="n">
         <v>193.894775390625</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>172.8580627441406</v>
+        <v>172.8580474853516</v>
       </c>
       <c r="C165" t="n">
         <v>194.7537994384766</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>172.7190551757812</v>
+        <v>172.7190704345703</v>
       </c>
       <c r="C166" t="n">
         <v>194.0174865722656</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>174.7947540283203</v>
+        <v>174.7948150634766</v>
       </c>
       <c r="C167" t="n">
         <v>196.3491363525391</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>176.5017242431641</v>
+        <v>176.501708984375</v>
       </c>
       <c r="C168" t="n">
         <v>198.2666015625</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>186.2634124755859</v>
+        <v>186.2634429931641</v>
       </c>
       <c r="C169" t="n">
         <v>208.5979461669922</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>188.4618682861328</v>
+        <v>188.4618377685547</v>
       </c>
       <c r="C170" t="n">
         <v>211.0599822998047</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>162.8751373291016</v>
+        <v>162.8752136230469</v>
       </c>
       <c r="C171" t="n">
         <v>182.4052734375</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>157.8836059570312</v>
+        <v>157.8835754394531</v>
       </c>
       <c r="C172" t="n">
         <v>176.2310180664062</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>173.5228729248047</v>
+        <v>173.5228576660156</v>
       </c>
       <c r="C173" t="n">
         <v>193.6876831054688</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>169.6748809814453</v>
+        <v>169.6748657226562</v>
       </c>
       <c r="C174" t="n">
         <v>189.3925476074219</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>164.9498291015625</v>
+        <v>164.9498596191406</v>
       </c>
       <c r="C175" t="n">
         <v>183.5174102783203</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>193.9524383544922</v>
+        <v>193.9524230957031</v>
       </c>
       <c r="C176" t="n">
         <v>215.7846374511719</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>167.3627319335938</v>
+        <v>167.3627471923828</v>
       </c>
       <c r="C177" t="n">
         <v>186.2018737792969</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>160.9499816894531</v>
+        <v>160.9499969482422</v>
       </c>
       <c r="C178" t="n">
         <v>178.4629516601562</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>159.8778228759766</v>
+        <v>159.8778533935547</v>
       </c>
       <c r="C179" t="n">
         <v>177.2741241455078</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>181.7138061523438</v>
+        <v>181.7138366699219</v>
       </c>
       <c r="C182" t="n">
         <v>200.7899932861328</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>167.3871765136719</v>
+        <v>167.3871612548828</v>
       </c>
       <c r="C183" t="n">
         <v>184.9593505859375</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>169.3465423583984</v>
+        <v>169.3465270996094</v>
       </c>
       <c r="C184" t="n">
         <v>186.4933319091797</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>173.2885437011719</v>
+        <v>173.2885894775391</v>
       </c>
       <c r="C185" t="n">
         <v>190.8344879150391</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>168.468994140625</v>
+        <v>168.4689483642578</v>
       </c>
       <c r="C186" t="n">
         <v>185.5269165039062</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>169.9632873535156</v>
+        <v>169.9632720947266</v>
       </c>
       <c r="C187" t="n">
         <v>186.5240020751953</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>178.7413330078125</v>
+        <v>178.7413482666016</v>
       </c>
       <c r="C188" t="n">
         <v>196.1573791503906</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>172.3562316894531</v>
+        <v>172.356201171875</v>
       </c>
       <c r="C190" t="n">
         <v>188.5411834716797</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>178.8210144042969</v>
+        <v>178.821044921875</v>
       </c>
       <c r="C194" t="n">
         <v>194.9225311279297</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>190.8812866210938</v>
+        <v>190.8813018798828</v>
       </c>
       <c r="C195" t="n">
         <v>208.0687255859375</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>187.7823181152344</v>
+        <v>187.7823333740234</v>
       </c>
       <c r="C196" t="n">
         <v>204.0190277099609</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>178.8659973144531</v>
+        <v>178.8659820556641</v>
       </c>
       <c r="C197" t="n">
         <v>194.3317565917969</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>185.09619140625</v>
+        <v>185.0961761474609</v>
       </c>
       <c r="C198" t="n">
         <v>201.1006317138672</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>178.9922027587891</v>
+        <v>178.9921875</v>
       </c>
       <c r="C199" t="n">
         <v>193.8128967285156</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>177.3803863525391</v>
+        <v>177.3803558349609</v>
       </c>
       <c r="C200" t="n">
         <v>192.0676116943359</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>183.2686004638672</v>
+        <v>183.2685852050781</v>
       </c>
       <c r="C201" t="n">
         <v>198.4433898925781</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>162.3302459716797</v>
+        <v>162.3302612304688</v>
       </c>
       <c r="C202" t="n">
         <v>175.1808166503906</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>171.9026184082031</v>
+        <v>171.9026641845703</v>
       </c>
       <c r="C203" t="n">
         <v>185.5110015869141</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>181.6426086425781</v>
+        <v>181.6425933837891</v>
       </c>
       <c r="C204" t="n">
         <v>196.0220184326172</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>185.9424285888672</v>
+        <v>185.9423980712891</v>
       </c>
       <c r="C205" t="n">
         <v>199.92138671875</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>171.5013427734375</v>
+        <v>171.5013732910156</v>
       </c>
       <c r="C207" t="n">
         <v>184.3946533203125</v>
@@ -6005,7 +6005,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>194.0122222900391</v>
+        <v>194.01220703125</v>
       </c>
       <c r="C209" t="n">
         <v>207.7908782958984</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>177.4597778320312</v>
+        <v>177.4597625732422</v>
       </c>
       <c r="C210" t="n">
         <v>190.0628967285156</v>
@@ -6063,7 +6063,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>194.4936828613281</v>
+        <v>194.4937286376953</v>
       </c>
       <c r="C211" t="n">
         <v>207.5550384521484</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>205.2567443847656</v>
+        <v>205.2567291259766</v>
       </c>
       <c r="C212" t="n">
         <v>219.0408782958984</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>191.1088409423828</v>
+        <v>191.1088562011719</v>
       </c>
       <c r="C214" t="n">
         <v>203.2468566894531</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>186.8583984375</v>
+        <v>186.8583831787109</v>
       </c>
       <c r="C215" t="n">
         <v>198.7264099121094</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>174.5874328613281</v>
+        <v>174.5874176025391</v>
       </c>
       <c r="C216" t="n">
         <v>185.6761016845703</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>180.9788970947266</v>
+        <v>180.9788665771484</v>
       </c>
       <c r="C217" t="n">
         <v>191.6902465820312</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>177.2528839111328</v>
+        <v>177.2528991699219</v>
       </c>
       <c r="C218" t="n">
         <v>187.7437133789062</v>
@@ -6295,7 +6295,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>174.8332061767578</v>
+        <v>174.8331909179688</v>
       </c>
       <c r="C219" t="n">
         <v>185.1808166503906</v>
@@ -6324,7 +6324,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>184.4093627929688</v>
+        <v>184.4093780517578</v>
       </c>
       <c r="C220" t="n">
         <v>194.5361633300781</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>174.8330383300781</v>
+        <v>174.8330230712891</v>
       </c>
       <c r="C221" t="n">
         <v>184.4339599609375</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>172.8730621337891</v>
+        <v>172.8730773925781</v>
       </c>
       <c r="C222" t="n">
         <v>182.3663482666016</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>181.3694000244141</v>
+        <v>181.3694305419922</v>
       </c>
       <c r="C225" t="n">
         <v>190.5738983154297</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>181.1288299560547</v>
+        <v>181.1288452148438</v>
       </c>
       <c r="C226" t="n">
         <v>189.5440216064453</v>
@@ -6527,7 +6527,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>175.4868621826172</v>
+        <v>175.4868927001953</v>
       </c>
       <c r="C227" t="n">
         <v>183.6399383544922</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>166.7046508789062</v>
+        <v>166.7046356201172</v>
       </c>
       <c r="C228" t="n">
         <v>174.4496917724609</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>170.2364044189453</v>
+        <v>170.2363739013672</v>
       </c>
       <c r="C231" t="n">
         <v>177.3034515380859</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>157.02880859375</v>
+        <v>157.0288238525391</v>
       </c>
       <c r="C233" t="n">
         <v>162.8066101074219</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>130.8687133789062</v>
+        <v>130.8687286376953</v>
       </c>
       <c r="C234" t="n">
         <v>135.6839599609375</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>135.9757995605469</v>
+        <v>135.9758148193359</v>
       </c>
       <c r="C236" t="n">
         <v>140.1336517333984</v>
@@ -6846,7 +6846,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>143.5563201904297</v>
+        <v>143.5563354492188</v>
       </c>
       <c r="C238" t="n">
         <v>147.1462249755859</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>137.0676422119141</v>
+        <v>137.0676574707031</v>
       </c>
       <c r="C239" t="n">
         <v>140.4952850341797</v>
@@ -6962,7 +6962,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>156.915283203125</v>
+        <v>156.9152984619141</v>
       </c>
       <c r="C242" t="n">
         <v>159.9685516357422</v>
@@ -7049,7 +7049,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>147.1289825439453</v>
+        <v>147.1289978027344</v>
       </c>
       <c r="C245" t="n">
         <v>149.0399932861328</v>
